--- a/data/trans_orig/IQ09_M-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ09_M-Clase-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio en meses que llevan sufriendo esa dolencia, enfermedad o impedimento que les haya limitado de forma continuada (más de 10 días en los últimos 12 meses)</t>
+          <t>Tiempo medio en meses que llevan sufriendo esa dolencia, enfermedad o impedimento que les haya limitado de forma continuada (más de 10 días en los últimos 12 meses) (tasa de respuesta: 97,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,7 +731,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,65</t>
+          <t>0,0; 0,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,41; 6,0</t>
+          <t>1,34; 5,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,05</t>
+          <t>0,0; 2,93</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,96; 5,31</t>
+          <t>0,91; 5,14</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,13</t>
+          <t>0,13; 1,1</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,0</t>
+          <t>0,0; 1,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,0</t>
+          <t>0,0; 6,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -886,17 +886,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,64</t>
+          <t>0,0; 4,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,68</t>
+          <t>0,0; 1,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,0</t>
+          <t>0,0; 6,62</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,16</t>
+          <t>0,0; 3,26</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,49</t>
+          <t>0,2; 1,51</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,09; 4,0</t>
+          <t>0,0; 4,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,71</t>
+          <t>0,0; 4,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,71</t>
+          <t>0,0; 4,25</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1046,12 +1046,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 3,44</t>
+          <t>0,0; 3,02</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,34</t>
+          <t>0,0; 5,46</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,03</t>
+          <t>0,0; 3,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,93</t>
+          <t>0,68; 2,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,32; 6,88</t>
+          <t>1,31; 6,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,02; 1,79</t>
+          <t>0,0; 1,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,05</t>
+          <t>0,0; 1,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,41</t>
+          <t>0,95; 3,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 2,91</t>
+          <t>0,19; 2,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,43</t>
+          <t>0,15; 1,34</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,13</t>
+          <t>0,24; 2,25</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,08; 2,7</t>
+          <t>1,04; 2,74</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,07; 4,51</t>
+          <t>0,97; 4,44</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,1</t>
+          <t>0,12; 1,01</t>
         </is>
       </c>
     </row>
@@ -1281,17 +1281,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,51</t>
+          <t>0,52; 3,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,11; 3,08</t>
+          <t>0,0; 2,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,67</t>
+          <t>0,0; 4,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 1,07</t>
+          <t>0,09; 1,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,98</t>
+          <t>1,04; 4,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1321,17 +1321,17 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,32</t>
+          <t>0,37; 2,28</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 2,47</t>
+          <t>0,09; 2,69</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,54</t>
+          <t>0,99; 3,58</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,29; 6,0</t>
+          <t>0,11; 6,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,74</t>
+          <t>0,0; 2,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1441,37 +1441,37 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,18</t>
+          <t>0,19; 3,18</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,18</t>
+          <t>0,0; 2,05</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,52</t>
+          <t>0,0; 0,56</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,57; 5,43</t>
+          <t>0,53; 5,59</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,11; 2,03</t>
+          <t>0,11; 2,23</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,73</t>
+          <t>0,3; 3,96</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,07; 1,54</t>
+          <t>0,07; 1,82</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,19; 2,25</t>
+          <t>0,24; 2,34</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,15</t>
+          <t>0,73; 2,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,1</t>
+          <t>0,69; 2,88</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,36</t>
+          <t>0,28; 1,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,37</t>
+          <t>0,51; 2,28</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,54</t>
+          <t>0,95; 2,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,66</t>
+          <t>0,94; 2,81</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,66; 1,95</t>
+          <t>0,59; 1,9</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,86</t>
+          <t>0,54; 1,88</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,02; 1,97</t>
+          <t>0,99; 1,96</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,08; 2,37</t>
+          <t>1,07; 2,34</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,46</t>
+          <t>0,57; 1,42</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ09_M-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ09_M-Clase-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,61</t>
+          <t>0,0; 0,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,05</t>
+          <t>0,0; 4,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,34; 5,55</t>
+          <t>1,1; 5,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,93</t>
+          <t>0,0; 2,92</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,91; 5,14</t>
+          <t>1,01; 5,41</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,1</t>
+          <t>0,13; 1,06</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,62</t>
+          <t>0,0; 9,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,65</t>
+          <t>0,0; 4,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,62</t>
+          <t>0,0; 9,0</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,26</t>
+          <t>0,0; 2,98</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,51</t>
+          <t>0,21; 1,55</t>
         </is>
       </c>
     </row>
@@ -1006,52 +1006,52 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>0,26; 4,0</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 3,0</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 4,79</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 6,0</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 4,79</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
           <t>0,0; 4,0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,0</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,25</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 6,0</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,25</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,0</t>
-        </is>
-      </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,02</t>
+          <t>0,0; 3,12</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,46</t>
+          <t>0,0; 5,57</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,53</t>
+          <t>0,0; 3,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,76</t>
+          <t>0,7; 2,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,31; 6,82</t>
+          <t>1,33; 6,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,72</t>
+          <t>0,0; 1,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,99</t>
+          <t>0,0; 1,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,35</t>
+          <t>0,92; 3,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 2,65</t>
+          <t>0,18; 2,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,34</t>
+          <t>0,14; 1,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,25</t>
+          <t>0,22; 2,21</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 2,74</t>
+          <t>1,05; 2,64</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,97; 4,44</t>
+          <t>1,02; 4,49</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,01</t>
+          <t>0,12; 1,09</t>
         </is>
       </c>
     </row>
@@ -1281,12 +1281,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,87</t>
+          <t>0,51; 3,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,18</t>
+          <t>0,11; 2,3</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 1,11</t>
+          <t>0,1; 1,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,04; 4,34</t>
+          <t>1,0; 4,11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1321,17 +1321,17 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,28</t>
+          <t>0,41; 2,38</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 2,69</t>
+          <t>0,09; 2,39</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,99; 3,58</t>
+          <t>0,95; 3,43</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,59</t>
+          <t>0,0; 2,74</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1441,37 +1441,37 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,19; 3,18</t>
+          <t>0,38; 2,82</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,05</t>
+          <t>0,0; 1,84</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,56</t>
+          <t>0,0; 0,59</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,53; 5,59</t>
+          <t>0,59; 5,69</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,11; 2,23</t>
+          <t>0,12; 2,08</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,96</t>
+          <t>0,17; 4,2</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,07; 1,82</t>
+          <t>0,14; 1,74</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,34</t>
+          <t>0,33; 2,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,12</t>
+          <t>0,77; 2,18</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,88</t>
+          <t>0,76; 2,88</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,37</t>
+          <t>0,28; 1,31</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,28</t>
+          <t>0,5; 2,28</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,45</t>
+          <t>0,98; 2,52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,81</t>
+          <t>0,94; 2,77</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,9</t>
+          <t>0,63; 1,81</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,54; 1,88</t>
+          <t>0,52; 1,93</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,99; 1,96</t>
+          <t>0,98; 1,97</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,07; 2,34</t>
+          <t>1,04; 2,42</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,42</t>
+          <t>0,57; 1,45</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ09_M-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ09_M-Clase-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,44 +648,44 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,04</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2,52</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3,57</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,95</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1,65</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0,21</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,04</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,52</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,57</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0,84</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
           <t>0,74</t>
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,45</t>
+          <t>0,48</t>
         </is>
       </c>
     </row>
@@ -716,47 +716,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 4,05</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2,0; 3,0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1,41; 6,0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 1,77</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>0,0; 3,0</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,63</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,03</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>2,0; 3,0</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1,1; 5,48</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,75</t>
+          <t>0,0; 0,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,92</t>
+          <t>0,0; 3,05</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,01; 5,41</t>
+          <t>0,96; 5,31</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,06</t>
+          <t>0,15; 1,19</t>
         </is>
       </c>
     </row>
@@ -788,49 +788,49 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2,02</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1,0</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,69</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0,67</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,98</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0,99</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>2,02</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,0</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,69</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0,71</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2,02</t>
-        </is>
-      </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
           <t>0,29</t>
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,81</t>
+          <t>0,79</t>
         </is>
       </c>
     </row>
@@ -856,49 +856,49 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0,0; 9,0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 4,64</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 1,67</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,64</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 2,0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>0,0; 9,0</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,49</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,87</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 9,0</t>
-        </is>
-      </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0,0; 0,79</t>
@@ -906,12 +906,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,98</t>
+          <t>0,0; 3,16</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,55</t>
+          <t>0,19; 1,45</t>
         </is>
       </c>
     </row>
@@ -928,49 +928,49 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,77</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4,0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2,97</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1,26</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>1,53</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,25</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1,12</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>1,77</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4,0</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2,62</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1,77</t>
-        </is>
-      </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
           <t>1,9</t>
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,2</t>
+          <t>2,37</t>
         </is>
       </c>
     </row>
@@ -996,47 +996,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 4,71</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 6,0</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>0,0; 4,0</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,26; 4,0</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0,09; 4,0</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>0,0; 3,0</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,79</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 6,0</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,79</t>
+          <t>0,0; 4,71</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1046,12 +1046,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,12</t>
+          <t>0,16; 3,44</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,57</t>
+          <t>0,0; 5,41</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,69</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1,81</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1,0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0,46</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>1,03</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1,52</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>3,74</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,48</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,69</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,81</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,0</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,49</t>
+          <t>1,12</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,49</t>
+          <t>0,72</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,33</t>
+          <t>0,0; 2,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,73</t>
+          <t>0,93; 3,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,33; 6,66</t>
+          <t>0,19; 2,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,86</t>
+          <t>0,12; 1,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,84</t>
+          <t>0,0; 4,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,45</t>
+          <t>0,73; 2,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 2,64</t>
+          <t>1,32; 6,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,23</t>
+          <t>0,26; 2,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,21</t>
+          <t>0,24; 2,13</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,05; 2,64</t>
+          <t>1,08; 2,7</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,02; 4,49</t>
+          <t>1,07; 4,51</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,09</t>
+          <t>0,31; 1,38</t>
         </is>
       </c>
     </row>
@@ -1213,44 +1213,44 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>0,47</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,84</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2,19</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
           <t>1,74</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>0,59</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,31</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1,36</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,47</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,84</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>2,24</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
           <t>1,11</t>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,94</t>
+          <t>1,9</t>
         </is>
       </c>
     </row>
@@ -1281,17 +1281,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,51; 3,74</t>
+          <t>0,08; 1,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,11; 2,3</t>
+          <t>0,0; 6,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,86</t>
+          <t>0,91; 3,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,12</t>
+          <t>0,53; 3,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,0</t>
+          <t>0,11; 3,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,11</t>
+          <t>0,0; 4,68</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1321,17 +1321,17 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,38</t>
+          <t>0,4; 2,32</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 2,39</t>
+          <t>0,1; 2,47</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,43</t>
+          <t>0,99; 3,43</t>
         </is>
       </c>
     </row>
@@ -1348,42 +1348,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2,79</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1,19</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0,64</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0,09</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>1,86</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>6,0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1,54</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2,79</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1,19</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,64</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0,11</t>
+          <t>1,45</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,67</t>
+          <t>0,63</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,11; 6,0</t>
+          <t>0,0; 7,24</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>0,38; 3,18</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 2,18</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 0,44</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0,29; 6,0</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,74</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 7,24</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>0,38; 2,82</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,84</t>
-        </is>
-      </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,59</t>
+          <t>0,0; 2,58</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,59; 5,69</t>
+          <t>0,57; 5,43</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,12; 2,08</t>
+          <t>0,11; 2,03</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,17; 4,2</t>
+          <t>0,31; 3,73</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,74</t>
+          <t>0,05; 1,46</t>
         </is>
       </c>
     </row>
@@ -1488,42 +1488,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1,17</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1,51</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1,68</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1,09</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>0,89</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>1,33</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>1,59</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,74</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,17</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,51</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,68</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>1,11</t>
+          <t>0,95</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,94</t>
+          <t>1,03</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,43</t>
+          <t>0,51; 2,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,18</t>
+          <t>0,95; 2,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,88</t>
+          <t>0,94; 2,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,31</t>
+          <t>0,65; 1,92</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,28</t>
+          <t>0,19; 2,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,52</t>
+          <t>0,77; 2,15</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,77</t>
+          <t>0,77; 3,1</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,63; 1,81</t>
+          <t>0,54; 1,61</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,93</t>
+          <t>0,55; 1,86</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,98; 1,97</t>
+          <t>1,02; 1,97</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,04; 2,42</t>
+          <t>1,08; 2,37</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,45</t>
+          <t>0,7; 1,57</t>
         </is>
       </c>
     </row>
